--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_17.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4475 +469,6825 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:52.526</t>
+          <t>2026-05-29 09:42:14.355</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779422034208</v>
+        <v>1780022530865</v>
       </c>
       <c r="C2" t="n">
-        <v>85255</v>
+        <v>83544</v>
       </c>
       <c r="D2" t="n">
-        <v>-416.46</v>
+        <v>552.86</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>947</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>105.12</v>
+        <v>299.19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3489</v>
+      </c>
+      <c r="L2" t="n">
+        <v>107</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.906</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:52.527</t>
+          <t>2026-05-29 09:42:14.356</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779422034410</v>
+        <v>1780022532504</v>
       </c>
       <c r="C3" t="n">
-        <v>85435</v>
+        <v>83819</v>
       </c>
       <c r="D3" t="n">
-        <v>-215.64</v>
+        <v>800.22</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>947</v>
+        <v>400</v>
       </c>
       <c r="G3" t="n">
-        <v>105.12</v>
+        <v>299.19</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1851</v>
+      </c>
+      <c r="L3" t="n">
+        <v>108</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.903</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:52.722</t>
+          <t>2026-05-29 09:42:14.357</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779422034611</v>
+        <v>1780022532704</v>
       </c>
       <c r="C4" t="n">
-        <v>85599</v>
+        <v>83837</v>
       </c>
       <c r="D4" t="n">
-        <v>-40.86</v>
+        <v>778.21</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>665</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>109.07</v>
+        <v>299.19</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1652</v>
+      </c>
+      <c r="L4" t="n">
+        <v>116</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.766</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:52.724</t>
+          <t>2026-05-29 09:42:14.751</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779422034812</v>
+        <v>1780022532904</v>
       </c>
       <c r="C5" t="n">
-        <v>85026</v>
+        <v>83688</v>
       </c>
       <c r="D5" t="n">
-        <v>-611.8200000000001</v>
+        <v>590.3</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>665</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>109.07</v>
+        <v>299.19</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1846</v>
+      </c>
+      <c r="L5" t="n">
+        <v>113</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.007</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:53.016</t>
+          <t>2026-05-29 09:42:14.752</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779422035014</v>
+        <v>1780022533104</v>
       </c>
       <c r="C6" t="n">
-        <v>85237</v>
+        <v>83689</v>
       </c>
       <c r="D6" t="n">
-        <v>-370.23</v>
+        <v>561.78</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>665</v>
+        <v>400</v>
       </c>
       <c r="G6" t="n">
-        <v>109.07</v>
+        <v>299.19</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1647</v>
+      </c>
+      <c r="L6" t="n">
+        <v>110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.032</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:53.340</t>
+          <t>2026-05-29 09:42:14.754</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779422035215</v>
+        <v>1780022533323</v>
       </c>
       <c r="C7" t="n">
-        <v>85447</v>
+        <v>83945</v>
       </c>
       <c r="D7" t="n">
-        <v>-141.71</v>
+        <v>789.6900000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>665</v>
+        <v>3757</v>
       </c>
       <c r="G7" t="n">
-        <v>109.07</v>
+        <v>299.19</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1430</v>
+      </c>
+      <c r="L7" t="n">
+        <v>111</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.974</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:53.341</t>
+          <t>2026-05-29 09:42:14.755</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779422035417</v>
+        <v>1780022533523</v>
       </c>
       <c r="C8" t="n">
-        <v>85326</v>
+        <v>83495</v>
       </c>
       <c r="D8" t="n">
-        <v>-255.63</v>
+        <v>300.21</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
-        <v>725</v>
+        <v>3757</v>
       </c>
       <c r="G8" t="n">
-        <v>109.9</v>
+        <v>299.19</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L8" t="n">
+        <v>109</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.912</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:53.342</t>
+          <t>2026-05-29 09:42:15.023</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779422035618</v>
+        <v>1780022533723</v>
       </c>
       <c r="C9" t="n">
-        <v>85018</v>
+        <v>83518</v>
       </c>
       <c r="D9" t="n">
-        <v>-550.85</v>
+        <v>308.2</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
-        <v>725</v>
+        <v>3757</v>
       </c>
       <c r="G9" t="n">
-        <v>109.9</v>
+        <v>299.19</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1298</v>
+      </c>
+      <c r="L9" t="n">
+        <v>115</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:54.071</t>
+          <t>2026-05-29 09:42:15.495</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779422035819</v>
+        <v>1780022533923</v>
       </c>
       <c r="C10" t="n">
-        <v>85246</v>
+        <v>83581</v>
       </c>
       <c r="D10" t="n">
-        <v>-295.3</v>
+        <v>355.79</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>725</v>
+        <v>3757</v>
       </c>
       <c r="G10" t="n">
-        <v>109.9</v>
+        <v>299.19</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1571</v>
+      </c>
+      <c r="L10" t="n">
+        <v>123</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.993</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:54.077</t>
+          <t>2026-05-29 09:42:15.496</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779422036021</v>
+        <v>1780022534344</v>
       </c>
       <c r="C11" t="n">
-        <v>85513</v>
+        <v>83292</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.54</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>705</v>
+        <v>1060</v>
       </c>
       <c r="G11" t="n">
-        <v>108.49</v>
+        <v>285.84</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1151</v>
+      </c>
+      <c r="L11" t="n">
+        <v>107</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.922</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:54.077</t>
+          <t>2026-05-29 09:42:15.498</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779422036222</v>
+        <v>1780022534543</v>
       </c>
       <c r="C12" t="n">
-        <v>84852</v>
+        <v>83191</v>
       </c>
       <c r="D12" t="n">
-        <v>-673.86</v>
+        <v>-54.45</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F12" t="n">
-        <v>705</v>
+        <v>1060</v>
       </c>
       <c r="G12" t="n">
-        <v>108.49</v>
+        <v>285.84</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>953</v>
+      </c>
+      <c r="L12" t="n">
+        <v>116</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.061</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:54.384</t>
+          <t>2026-05-29 09:42:15.841</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779422036424</v>
+        <v>1780022534744</v>
       </c>
       <c r="C13" t="n">
-        <v>85068</v>
+        <v>83434</v>
       </c>
       <c r="D13" t="n">
-        <v>-424.17</v>
+        <v>191.27</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>705</v>
+        <v>1060</v>
       </c>
       <c r="G13" t="n">
-        <v>108.49</v>
+        <v>285.84</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1096</v>
+      </c>
+      <c r="L13" t="n">
+        <v>107</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:54.390</t>
+          <t>2026-05-29 09:42:17.773</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779422036625</v>
+        <v>1780022534962</v>
       </c>
       <c r="C14" t="n">
-        <v>85332</v>
+        <v>83156</v>
       </c>
       <c r="D14" t="n">
-        <v>-138.96</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F14" t="n">
-        <v>705</v>
+        <v>1060</v>
       </c>
       <c r="G14" t="n">
-        <v>108.49</v>
+        <v>285.84</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2810</v>
+      </c>
+      <c r="L14" t="n">
+        <v>110</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:55.000</t>
+          <t>2026-05-29 09:42:17.804</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779422036827</v>
+        <v>1780022535162</v>
       </c>
       <c r="C15" t="n">
-        <v>85350</v>
+        <v>83101</v>
       </c>
       <c r="D15" t="n">
-        <v>-114.01</v>
+        <v>-146.48</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F15" t="n">
-        <v>705</v>
+        <v>1060</v>
       </c>
       <c r="G15" t="n">
-        <v>109.49</v>
+        <v>285.84</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2641</v>
+      </c>
+      <c r="L15" t="n">
+        <v>123</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:55.001</t>
+          <t>2026-05-29 09:42:17.832</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779422037028</v>
+        <v>1780022535362</v>
       </c>
       <c r="C16" t="n">
-        <v>84907</v>
+        <v>83139</v>
       </c>
       <c r="D16" t="n">
-        <v>-551.3099999999999</v>
+        <v>-101.15</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>705</v>
+        <v>1060</v>
       </c>
       <c r="G16" t="n">
-        <v>109.49</v>
+        <v>285.84</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2469</v>
+      </c>
+      <c r="L16" t="n">
+        <v>107</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.838</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:55.002</t>
+          <t>2026-05-29 09:42:17.842</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779422037229</v>
+        <v>1780022535563</v>
       </c>
       <c r="C17" t="n">
-        <v>85166</v>
+        <v>83525</v>
       </c>
       <c r="D17" t="n">
-        <v>-264.75</v>
+        <v>289.9</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>705</v>
+        <v>1060</v>
       </c>
       <c r="G17" t="n">
-        <v>109.49</v>
+        <v>285.84</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2278</v>
+      </c>
+      <c r="L17" t="n">
+        <v>106</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.523</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:55.382</t>
+          <t>2026-05-29 09:42:17.881</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779422037431</v>
+        <v>1780022535762</v>
       </c>
       <c r="C18" t="n">
-        <v>85432</v>
+        <v>83290</v>
       </c>
       <c r="D18" t="n">
-        <v>14.49</v>
+        <v>40.41</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>685</v>
+        <v>1259</v>
       </c>
       <c r="G18" t="n">
-        <v>102.49</v>
+        <v>323.96</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2118</v>
+      </c>
+      <c r="L18" t="n">
+        <v>113</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.172</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:55.383</t>
+          <t>2026-05-29 09:42:17.902</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779422037632</v>
+        <v>1780022535962</v>
       </c>
       <c r="C19" t="n">
-        <v>84935</v>
+        <v>83095</v>
       </c>
       <c r="D19" t="n">
-        <v>-483.23</v>
+        <v>-156.61</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>685</v>
+        <v>1259</v>
       </c>
       <c r="G19" t="n">
-        <v>102.49</v>
+        <v>323.96</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1940</v>
+      </c>
+      <c r="L19" t="n">
+        <v>112</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:55.828</t>
+          <t>2026-05-29 09:42:17.904</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779422037834</v>
+        <v>1780022536162</v>
       </c>
       <c r="C20" t="n">
-        <v>85248</v>
+        <v>83320</v>
       </c>
       <c r="D20" t="n">
-        <v>-146.07</v>
+        <v>76.22</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F20" t="n">
-        <v>685</v>
+        <v>1259</v>
       </c>
       <c r="G20" t="n">
-        <v>102.49</v>
+        <v>323.96</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1741</v>
+      </c>
+      <c r="L20" t="n">
+        <v>108</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:55.853</t>
+          <t>2026-05-29 09:42:17.906</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779422038035</v>
+        <v>1780022536381</v>
       </c>
       <c r="C21" t="n">
-        <v>85551</v>
+        <v>83578</v>
       </c>
       <c r="D21" t="n">
-        <v>164.23</v>
+        <v>330.41</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F21" t="n">
-        <v>604</v>
+        <v>739</v>
       </c>
       <c r="G21" t="n">
-        <v>93.69</v>
+        <v>303.04</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1524</v>
+      </c>
+      <c r="L21" t="n">
+        <v>117</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:56.229</t>
+          <t>2026-05-29 09:42:17.907</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779422038236</v>
+        <v>1780022536581</v>
       </c>
       <c r="C22" t="n">
-        <v>85214</v>
+        <v>83585</v>
       </c>
       <c r="D22" t="n">
-        <v>-180.98</v>
+        <v>320.89</v>
       </c>
       <c r="E22" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F22" t="n">
-        <v>604</v>
+        <v>739</v>
       </c>
       <c r="G22" t="n">
-        <v>93.69</v>
+        <v>303.04</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L22" t="n">
+        <v>110</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.865</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:56.230</t>
+          <t>2026-05-29 09:42:17.908</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779422038438</v>
+        <v>1780022536781</v>
       </c>
       <c r="C23" t="n">
-        <v>85309</v>
+        <v>83425</v>
       </c>
       <c r="D23" t="n">
-        <v>-76.93000000000001</v>
+        <v>144.84</v>
       </c>
       <c r="E23" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>604</v>
+        <v>739</v>
       </c>
       <c r="G23" t="n">
-        <v>93.69</v>
+        <v>303.04</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1126</v>
+      </c>
+      <c r="L23" t="n">
+        <v>109</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:56.625</t>
+          <t>2026-05-29 09:42:18.115</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779422038639</v>
+        <v>1780022536981</v>
       </c>
       <c r="C24" t="n">
-        <v>85635</v>
+        <v>83503</v>
       </c>
       <c r="D24" t="n">
-        <v>252.92</v>
+        <v>215.6</v>
       </c>
       <c r="E24" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F24" t="n">
-        <v>604</v>
+        <v>739</v>
       </c>
       <c r="G24" t="n">
-        <v>93.69</v>
+        <v>303.04</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L24" t="n">
+        <v>106</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.293</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:56.632</t>
+          <t>2026-05-29 09:42:18.118</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779422038841</v>
+        <v>1780022537181</v>
       </c>
       <c r="C25" t="n">
-        <v>85949</v>
+        <v>83501</v>
       </c>
       <c r="D25" t="n">
-        <v>554.27</v>
+        <v>202.82</v>
       </c>
       <c r="E25" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F25" t="n">
-        <v>685</v>
+        <v>739</v>
       </c>
       <c r="G25" t="n">
-        <v>95.02</v>
+        <v>303.04</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K25" t="n">
+        <v>936</v>
+      </c>
+      <c r="L25" t="n">
+        <v>110</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.621</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:57.024</t>
+          <t>2026-05-29 09:42:18.119</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779422039042</v>
+        <v>1780022537381</v>
       </c>
       <c r="C26" t="n">
-        <v>85355</v>
+        <v>83628</v>
       </c>
       <c r="D26" t="n">
-        <v>-67.44</v>
+        <v>319.68</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F26" t="n">
-        <v>685</v>
+        <v>880</v>
       </c>
       <c r="G26" t="n">
-        <v>95.02</v>
+        <v>295.02</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>737</v>
+      </c>
+      <c r="L26" t="n">
+        <v>145</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.954</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:57.025</t>
+          <t>2026-05-29 09:42:18.524</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779422039244</v>
+        <v>1780022537581</v>
       </c>
       <c r="C27" t="n">
-        <v>85618</v>
+        <v>83547</v>
       </c>
       <c r="D27" t="n">
-        <v>198.93</v>
+        <v>222.7</v>
       </c>
       <c r="E27" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F27" t="n">
-        <v>685</v>
+        <v>880</v>
       </c>
       <c r="G27" t="n">
-        <v>95.02</v>
+        <v>295.02</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K27" t="n">
+        <v>942</v>
+      </c>
+      <c r="L27" t="n">
+        <v>111</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:57.444</t>
+          <t>2026-05-29 09:42:18.527</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779422039445</v>
+        <v>1780022537781</v>
       </c>
       <c r="C28" t="n">
-        <v>85910</v>
+        <v>83621</v>
       </c>
       <c r="D28" t="n">
-        <v>480.98</v>
+        <v>285.56</v>
       </c>
       <c r="E28" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F28" t="n">
-        <v>765</v>
+        <v>520</v>
       </c>
       <c r="G28" t="n">
-        <v>93.90000000000001</v>
+        <v>307.79</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>746</v>
+      </c>
+      <c r="L28" t="n">
+        <v>106</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.793</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:57.446</t>
+          <t>2026-05-29 09:42:18.960</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779422039646</v>
+        <v>1780022538000</v>
       </c>
       <c r="C29" t="n">
-        <v>86235</v>
+        <v>83880</v>
       </c>
       <c r="D29" t="n">
-        <v>781.9299999999999</v>
+        <v>530.28</v>
       </c>
       <c r="E29" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F29" t="n">
-        <v>765</v>
+        <v>520</v>
       </c>
       <c r="G29" t="n">
-        <v>93.90000000000001</v>
+        <v>307.79</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K29" t="n">
+        <v>959</v>
+      </c>
+      <c r="L29" t="n">
+        <v>108</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:57.858</t>
+          <t>2026-05-29 09:42:18.961</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779422039848</v>
+        <v>1780022538200</v>
       </c>
       <c r="C30" t="n">
-        <v>85676</v>
+        <v>83785</v>
       </c>
       <c r="D30" t="n">
-        <v>183.84</v>
+        <v>408.77</v>
       </c>
       <c r="E30" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F30" t="n">
-        <v>765</v>
+        <v>520</v>
       </c>
       <c r="G30" t="n">
-        <v>93.90000000000001</v>
+        <v>307.79</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>761</v>
+      </c>
+      <c r="L30" t="n">
+        <v>128</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.678</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:57.864</t>
+          <t>2026-05-29 09:42:19.312</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779422040049</v>
+        <v>1780022538400</v>
       </c>
       <c r="C31" t="n">
-        <v>85868</v>
+        <v>83909</v>
       </c>
       <c r="D31" t="n">
-        <v>366.64</v>
+        <v>512.33</v>
       </c>
       <c r="E31" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F31" t="n">
-        <v>765</v>
+        <v>520</v>
       </c>
       <c r="G31" t="n">
-        <v>93.90000000000001</v>
+        <v>307.79</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K31" t="n">
+        <v>911</v>
+      </c>
+      <c r="L31" t="n">
+        <v>111</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.784</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:58.359</t>
+          <t>2026-05-29 09:42:19.313</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779422040251</v>
+        <v>1780022538600</v>
       </c>
       <c r="C32" t="n">
-        <v>86045</v>
+        <v>83567</v>
       </c>
       <c r="D32" t="n">
-        <v>525.3099999999999</v>
+        <v>144.71</v>
       </c>
       <c r="E32" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F32" t="n">
-        <v>765</v>
+        <v>520</v>
       </c>
       <c r="G32" t="n">
-        <v>93.90000000000001</v>
+        <v>307.79</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>712</v>
+      </c>
+      <c r="L32" t="n">
+        <v>107</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:58.360</t>
+          <t>2026-05-29 09:42:19.810</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779422040452</v>
+        <v>1780022538800</v>
       </c>
       <c r="C33" t="n">
-        <v>86289</v>
+        <v>83526</v>
       </c>
       <c r="D33" t="n">
-        <v>743.05</v>
+        <v>96.48</v>
       </c>
       <c r="E33" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F33" t="n">
-        <v>846</v>
+        <v>520</v>
       </c>
       <c r="G33" t="n">
-        <v>98.37</v>
+        <v>307.79</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1009</v>
+      </c>
+      <c r="L33" t="n">
+        <v>112</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.772</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:58.681</t>
+          <t>2026-05-29 09:42:19.821</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779422040653</v>
+        <v>1780022539000</v>
       </c>
       <c r="C34" t="n">
-        <v>85742</v>
+        <v>83175</v>
       </c>
       <c r="D34" t="n">
-        <v>158.89</v>
+        <v>-259.35</v>
       </c>
       <c r="E34" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F34" t="n">
-        <v>846</v>
+        <v>520</v>
       </c>
       <c r="G34" t="n">
-        <v>98.37</v>
+        <v>307.79</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>819</v>
+      </c>
+      <c r="L34" t="n">
+        <v>107</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.994</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:58.682</t>
+          <t>2026-05-29 09:42:20.352</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779422040855</v>
+        <v>1780022539200</v>
       </c>
       <c r="C35" t="n">
-        <v>85947</v>
+        <v>83222</v>
       </c>
       <c r="D35" t="n">
-        <v>355.95</v>
+        <v>-199.38</v>
       </c>
       <c r="E35" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F35" t="n">
-        <v>846</v>
+        <v>520</v>
       </c>
       <c r="G35" t="n">
-        <v>98.37</v>
+        <v>307.79</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1151</v>
+      </c>
+      <c r="L35" t="n">
+        <v>111</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.612</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:59.072</t>
+          <t>2026-05-29 09:42:20.397</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779422041056</v>
+        <v>1780022539419</v>
       </c>
       <c r="C36" t="n">
-        <v>86145</v>
+        <v>83393</v>
       </c>
       <c r="D36" t="n">
-        <v>536.15</v>
+        <v>-18.41</v>
       </c>
       <c r="E36" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F36" t="n">
-        <v>846</v>
+        <v>520</v>
       </c>
       <c r="G36" t="n">
-        <v>98.37</v>
+        <v>307.79</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>977</v>
+      </c>
+      <c r="L36" t="n">
+        <v>106</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:59.074</t>
+          <t>2026-05-29 09:42:20.884</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779422041258</v>
+        <v>1780022539619</v>
       </c>
       <c r="C37" t="n">
-        <v>86393</v>
+        <v>84387</v>
       </c>
       <c r="D37" t="n">
-        <v>757.34</v>
+        <v>976.51</v>
       </c>
       <c r="E37" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F37" t="n">
-        <v>846</v>
+        <v>1838</v>
       </c>
       <c r="G37" t="n">
-        <v>76.8</v>
+        <v>307.79</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1264</v>
+      </c>
+      <c r="L37" t="n">
+        <v>118</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:59.482</t>
+          <t>2026-05-29 09:42:20.885</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779422041459</v>
+        <v>1780022539819</v>
       </c>
       <c r="C38" t="n">
-        <v>85885</v>
+        <v>84133</v>
       </c>
       <c r="D38" t="n">
-        <v>211.48</v>
+        <v>673.6900000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F38" t="n">
-        <v>846</v>
+        <v>1838</v>
       </c>
       <c r="G38" t="n">
-        <v>76.8</v>
+        <v>307.79</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1065</v>
+      </c>
+      <c r="L38" t="n">
+        <v>111</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.056</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:59.487</t>
+          <t>2026-05-29 09:42:22.795</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779422041660</v>
+        <v>1780022540019</v>
       </c>
       <c r="C39" t="n">
-        <v>86097</v>
+        <v>84683</v>
       </c>
       <c r="D39" t="n">
-        <v>412.9</v>
+        <v>1190</v>
       </c>
       <c r="E39" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F39" t="n">
-        <v>846</v>
+        <v>1838</v>
       </c>
       <c r="G39" t="n">
-        <v>76.8</v>
+        <v>307.79</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2775</v>
+      </c>
+      <c r="L39" t="n">
+        <v>145</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.803</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:00.235</t>
+          <t>2026-05-29 09:42:22.796</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779422041862</v>
+        <v>1780022540219</v>
       </c>
       <c r="C40" t="n">
-        <v>86382</v>
+        <v>84767</v>
       </c>
       <c r="D40" t="n">
-        <v>677.26</v>
+        <v>1214.5</v>
       </c>
       <c r="E40" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F40" t="n">
-        <v>725</v>
+        <v>1838</v>
       </c>
       <c r="G40" t="n">
-        <v>74.05</v>
+        <v>307.79</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2576</v>
+      </c>
+      <c r="L40" t="n">
+        <v>108</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.635</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:00.236</t>
+          <t>2026-05-29 09:42:22.797</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779422042063</v>
+        <v>1780022540419</v>
       </c>
       <c r="C41" t="n">
-        <v>86705</v>
+        <v>85113</v>
       </c>
       <c r="D41" t="n">
-        <v>966.4</v>
+        <v>1499.78</v>
       </c>
       <c r="E41" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F41" t="n">
-        <v>725</v>
+        <v>1838</v>
       </c>
       <c r="G41" t="n">
-        <v>74.05</v>
+        <v>307.79</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2377</v>
+      </c>
+      <c r="L41" t="n">
+        <v>108</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.518</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:00.238</t>
+          <t>2026-05-29 09:42:22.798</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779422042265</v>
+        <v>1780022540619</v>
       </c>
       <c r="C42" t="n">
-        <v>86158</v>
+        <v>85549</v>
       </c>
       <c r="D42" t="n">
-        <v>371.08</v>
+        <v>1860.79</v>
       </c>
       <c r="E42" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F42" t="n">
-        <v>725</v>
+        <v>1838</v>
       </c>
       <c r="G42" t="n">
-        <v>74.05</v>
+        <v>307.79</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2178</v>
+      </c>
+      <c r="L42" t="n">
+        <v>108</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.597</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:00.240</t>
+          <t>2026-05-29 09:42:24.187</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779422042466</v>
+        <v>1780022540819</v>
       </c>
       <c r="C43" t="n">
-        <v>86332</v>
+        <v>84285</v>
       </c>
       <c r="D43" t="n">
-        <v>526.52</v>
+        <v>503.75</v>
       </c>
       <c r="E43" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F43" t="n">
-        <v>725</v>
+        <v>1838</v>
       </c>
       <c r="G43" t="n">
-        <v>74.05</v>
+        <v>307.79</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3367</v>
+      </c>
+      <c r="L43" t="n">
+        <v>110</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:00.504</t>
+          <t>2026-05-29 09:42:24.189</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779422042668</v>
+        <v>1780022541019</v>
       </c>
       <c r="C44" t="n">
-        <v>86419</v>
+        <v>82579</v>
       </c>
       <c r="D44" t="n">
-        <v>587.2</v>
+        <v>-1227.44</v>
       </c>
       <c r="E44" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F44" t="n">
-        <v>725</v>
+        <v>1838</v>
       </c>
       <c r="G44" t="n">
-        <v>74.05</v>
+        <v>307.79</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J44" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3169</v>
+      </c>
+      <c r="L44" t="n">
+        <v>124</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:00.947</t>
+          <t>2026-05-29 09:42:24.189</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779422042869</v>
+        <v>1780022541238</v>
       </c>
       <c r="C45" t="n">
-        <v>86619</v>
+        <v>82623</v>
       </c>
       <c r="D45" t="n">
-        <v>757.84</v>
+        <v>-1122.07</v>
       </c>
       <c r="E45" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F45" t="n">
-        <v>906</v>
+        <v>1838</v>
       </c>
       <c r="G45" t="n">
-        <v>92.70999999999999</v>
+        <v>307.79</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J45" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2951</v>
+      </c>
+      <c r="L45" t="n">
+        <v>123</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:00.948</t>
+          <t>2026-05-29 09:42:24.191</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779422043070</v>
+        <v>1780022541438</v>
       </c>
       <c r="C46" t="n">
-        <v>86114</v>
+        <v>83407</v>
       </c>
       <c r="D46" t="n">
-        <v>214.94</v>
+        <v>-281.96</v>
       </c>
       <c r="E46" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F46" t="n">
-        <v>906</v>
+        <v>1838</v>
       </c>
       <c r="G46" t="n">
-        <v>92.70999999999999</v>
+        <v>307.79</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J46" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2752</v>
+      </c>
+      <c r="L46" t="n">
+        <v>111</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:01.345</t>
+          <t>2026-05-29 09:42:24.192</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779422043272</v>
+        <v>1780022542338</v>
       </c>
       <c r="C47" t="n">
-        <v>86263</v>
+        <v>82302</v>
       </c>
       <c r="D47" t="n">
-        <v>353.2</v>
+        <v>-1372.87</v>
       </c>
       <c r="E47" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F47" t="n">
-        <v>906</v>
+        <v>1838</v>
       </c>
       <c r="G47" t="n">
-        <v>92.70999999999999</v>
+        <v>307.79</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1853</v>
+      </c>
+      <c r="L47" t="n">
+        <v>107</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.859</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:01.377</t>
+          <t>2026-05-29 09:42:24.193</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779422043473</v>
+        <v>1780022542538</v>
       </c>
       <c r="C48" t="n">
-        <v>86469</v>
+        <v>81680</v>
       </c>
       <c r="D48" t="n">
-        <v>541.54</v>
+        <v>-1926.22</v>
       </c>
       <c r="E48" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F48" t="n">
-        <v>906</v>
+        <v>1838</v>
       </c>
       <c r="G48" t="n">
-        <v>92.70999999999999</v>
+        <v>307.79</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1654</v>
+      </c>
+      <c r="L48" t="n">
+        <v>124</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.892</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:01.753</t>
+          <t>2026-05-29 09:42:24.381</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779422043675</v>
+        <v>1780022542738</v>
       </c>
       <c r="C49" t="n">
-        <v>86647</v>
+        <v>80684</v>
       </c>
       <c r="D49" t="n">
-        <v>692.46</v>
+        <v>-2825.91</v>
       </c>
       <c r="E49" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F49" t="n">
-        <v>766</v>
+        <v>1838</v>
       </c>
       <c r="G49" t="n">
-        <v>91.62</v>
+        <v>307.79</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>51.81</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1641</v>
+      </c>
+      <c r="L49" t="n">
+        <v>113</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.731</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:01.755</t>
+          <t>2026-05-29 09:42:24.452</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779422043876</v>
+        <v>1780022542957</v>
       </c>
       <c r="C50" t="n">
-        <v>86179</v>
+        <v>80717</v>
       </c>
       <c r="D50" t="n">
-        <v>189.84</v>
+        <v>-2651.62</v>
       </c>
       <c r="E50" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F50" t="n">
-        <v>766</v>
+        <v>1838</v>
       </c>
       <c r="G50" t="n">
-        <v>91.62</v>
+        <v>307.79</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1494</v>
+      </c>
+      <c r="L50" t="n">
+        <v>120</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.017</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:02.150</t>
+          <t>2026-05-29 09:42:24.453</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779422044077</v>
+        <v>1780022543157</v>
       </c>
       <c r="C51" t="n">
-        <v>86281</v>
+        <v>80593</v>
       </c>
       <c r="D51" t="n">
-        <v>282.35</v>
+        <v>-2643.04</v>
       </c>
       <c r="E51" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F51" t="n">
-        <v>766</v>
+        <v>1838</v>
       </c>
       <c r="G51" t="n">
-        <v>91.62</v>
+        <v>307.79</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1295</v>
+      </c>
+      <c r="L51" t="n">
+        <v>108</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:02.151</t>
+          <t>2026-05-29 09:42:24.454</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779422044279</v>
+        <v>1780022543357</v>
       </c>
       <c r="C52" t="n">
-        <v>86554</v>
+        <v>80086</v>
       </c>
       <c r="D52" t="n">
-        <v>541.23</v>
+        <v>-3017.88</v>
       </c>
       <c r="E52" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F52" t="n">
-        <v>766</v>
+        <v>1838</v>
       </c>
       <c r="G52" t="n">
-        <v>91.62</v>
+        <v>307.79</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1096</v>
+      </c>
+      <c r="L52" t="n">
+        <v>115</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.866</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:02.544</t>
+          <t>2026-05-29 09:42:24.850</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779422044480</v>
+        <v>1780022543557</v>
       </c>
       <c r="C53" t="n">
-        <v>86487</v>
+        <v>80779</v>
       </c>
       <c r="D53" t="n">
-        <v>447.17</v>
+        <v>-2173.99</v>
       </c>
       <c r="E53" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F53" t="n">
-        <v>785</v>
+        <v>1838</v>
       </c>
       <c r="G53" t="n">
-        <v>90.42</v>
+        <v>307.79</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1292</v>
+      </c>
+      <c r="L53" t="n">
+        <v>118</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:02.545</t>
+          <t>2026-05-29 09:42:24.882</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779422044682</v>
+        <v>1780022543757</v>
       </c>
       <c r="C54" t="n">
-        <v>86370</v>
+        <v>81746</v>
       </c>
       <c r="D54" t="n">
-        <v>307.81</v>
+        <v>-1098.29</v>
       </c>
       <c r="E54" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F54" t="n">
-        <v>785</v>
+        <v>1838</v>
       </c>
       <c r="G54" t="n">
-        <v>90.42</v>
+        <v>307.79</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L54" t="n">
+        <v>124</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.503</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:02.964</t>
+          <t>2026-05-29 09:42:24.884</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779422044883</v>
+        <v>1780022543958</v>
       </c>
       <c r="C55" t="n">
-        <v>86281</v>
+        <v>80748</v>
       </c>
       <c r="D55" t="n">
-        <v>203.42</v>
+        <v>-2041.38</v>
       </c>
       <c r="E55" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F55" t="n">
-        <v>785</v>
+        <v>1838</v>
       </c>
       <c r="G55" t="n">
-        <v>90.42</v>
+        <v>307.79</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K55" t="n">
+        <v>924</v>
+      </c>
+      <c r="L55" t="n">
+        <v>105</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.402</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:02.965</t>
+          <t>2026-05-29 09:42:25.284</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779422045085</v>
+        <v>1780022544157</v>
       </c>
       <c r="C56" t="n">
-        <v>86507</v>
+        <v>81610</v>
       </c>
       <c r="D56" t="n">
-        <v>419.25</v>
+        <v>-1077.31</v>
       </c>
       <c r="E56" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F56" t="n">
-        <v>785</v>
+        <v>1838</v>
       </c>
       <c r="G56" t="n">
-        <v>90.42</v>
+        <v>307.79</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1126</v>
+      </c>
+      <c r="L56" t="n">
+        <v>109</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:03.371</t>
+          <t>2026-05-29 09:42:25.310</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779422045286</v>
+        <v>1780022544357</v>
       </c>
       <c r="C57" t="n">
-        <v>86535</v>
+        <v>81640</v>
       </c>
       <c r="D57" t="n">
-        <v>426.28</v>
+        <v>-993.4400000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F57" t="n">
-        <v>866</v>
+        <v>1838</v>
       </c>
       <c r="G57" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K57" t="n">
+        <v>952</v>
+      </c>
+      <c r="L57" t="n">
+        <v>106</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:03.373</t>
+          <t>2026-05-29 09:42:25.366</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779422045487</v>
+        <v>1780022544557</v>
       </c>
       <c r="C58" t="n">
-        <v>86288</v>
+        <v>81531</v>
       </c>
       <c r="D58" t="n">
-        <v>157.97</v>
+        <v>-1052.77</v>
       </c>
       <c r="E58" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F58" t="n">
-        <v>866</v>
+        <v>1838</v>
       </c>
       <c r="G58" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K58" t="n">
+        <v>808</v>
+      </c>
+      <c r="L58" t="n">
+        <v>106</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.696</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:03.889</t>
+          <t>2026-05-29 09:42:26.363</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779422045689</v>
+        <v>1780022544776</v>
       </c>
       <c r="C59" t="n">
-        <v>86500</v>
+        <v>81059</v>
       </c>
       <c r="D59" t="n">
-        <v>362.07</v>
+        <v>-1472.13</v>
       </c>
       <c r="E59" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F59" t="n">
-        <v>866</v>
+        <v>1838</v>
       </c>
       <c r="G59" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1586</v>
+      </c>
+      <c r="L59" t="n">
+        <v>110</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.953</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:03.918</t>
+          <t>2026-05-29 09:42:26.572</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779422045890</v>
+        <v>1780022544977</v>
       </c>
       <c r="C60" t="n">
-        <v>86889</v>
+        <v>80508</v>
       </c>
       <c r="D60" t="n">
-        <v>732.97</v>
+        <v>-1949.52</v>
       </c>
       <c r="E60" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F60" t="n">
-        <v>604</v>
+        <v>1838</v>
       </c>
       <c r="G60" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1594</v>
+      </c>
+      <c r="L60" t="n">
+        <v>108</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.832</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:03.920</t>
+          <t>2026-05-29 09:42:26.667</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779422046092</v>
+        <v>1780022545176</v>
       </c>
       <c r="C61" t="n">
-        <v>86971</v>
+        <v>80692</v>
       </c>
       <c r="D61" t="n">
-        <v>778.3200000000001</v>
+        <v>-1668.05</v>
       </c>
       <c r="E61" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F61" t="n">
-        <v>604</v>
+        <v>1838</v>
       </c>
       <c r="G61" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1491</v>
+      </c>
+      <c r="L61" t="n">
+        <v>107</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.711</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:04.198</t>
+          <t>2026-05-29 09:42:26.716</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779422046293</v>
+        <v>1780022545376</v>
       </c>
       <c r="C62" t="n">
-        <v>86424</v>
+        <v>80471</v>
       </c>
       <c r="D62" t="n">
-        <v>192.4</v>
+        <v>-1805.65</v>
       </c>
       <c r="E62" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F62" t="n">
-        <v>604</v>
+        <v>1838</v>
       </c>
       <c r="G62" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1339</v>
+      </c>
+      <c r="L62" t="n">
+        <v>104</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.164</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:04.493</t>
+          <t>2026-05-29 09:42:26.718</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779422046494</v>
+        <v>1780022545576</v>
       </c>
       <c r="C63" t="n">
-        <v>86553</v>
+        <v>80697</v>
       </c>
       <c r="D63" t="n">
-        <v>311.78</v>
+        <v>-1489.36</v>
       </c>
       <c r="E63" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F63" t="n">
-        <v>604</v>
+        <v>1838</v>
       </c>
       <c r="G63" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L63" t="n">
+        <v>117</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.217</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:04.517</t>
+          <t>2026-05-29 09:42:27.096</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779422046696</v>
+        <v>1780022545776</v>
       </c>
       <c r="C64" t="n">
-        <v>86857</v>
+        <v>80802</v>
       </c>
       <c r="D64" t="n">
-        <v>600.1900000000001</v>
+        <v>-1309.9</v>
       </c>
       <c r="E64" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F64" t="n">
-        <v>604</v>
+        <v>1838</v>
       </c>
       <c r="G64" t="n">
-        <v>91.56</v>
+        <v>307.79</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1318</v>
+      </c>
+      <c r="L64" t="n">
+        <v>98</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.505</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:04.855</t>
+          <t>2026-05-29 09:42:27.097</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779422046897</v>
+        <v>1780022545976</v>
       </c>
       <c r="C65" t="n">
-        <v>87020</v>
+        <v>80733</v>
       </c>
       <c r="D65" t="n">
-        <v>733.1799999999999</v>
+        <v>-1313.4</v>
       </c>
       <c r="E65" t="n">
         <v>77</v>
       </c>
       <c r="F65" t="n">
-        <v>927</v>
+        <v>6257</v>
       </c>
       <c r="G65" t="n">
-        <v>95.73</v>
+        <v>307.79</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L65" t="n">
+        <v>116</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.094</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:05.210</t>
+          <t>2026-05-29 09:42:27.098</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779422047099</v>
+        <v>1780022546196</v>
       </c>
       <c r="C66" t="n">
-        <v>86534</v>
+        <v>80674</v>
       </c>
       <c r="D66" t="n">
-        <v>210.53</v>
+        <v>-1306.73</v>
       </c>
       <c r="E66" t="n">
         <v>77</v>
       </c>
       <c r="F66" t="n">
-        <v>927</v>
+        <v>6257</v>
       </c>
       <c r="G66" t="n">
-        <v>95.73</v>
+        <v>307.79</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K66" t="n">
+        <v>901</v>
+      </c>
+      <c r="L66" t="n">
+        <v>107</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.755</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:05.211</t>
+          <t>2026-05-29 09:42:27.709</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779422047300</v>
+        <v>1780022546395</v>
       </c>
       <c r="C67" t="n">
-        <v>86646</v>
+        <v>80834</v>
       </c>
       <c r="D67" t="n">
-        <v>312</v>
+        <v>-1081.39</v>
       </c>
       <c r="E67" t="n">
         <v>77</v>
       </c>
       <c r="F67" t="n">
-        <v>927</v>
+        <v>6257</v>
       </c>
       <c r="G67" t="n">
-        <v>95.73</v>
+        <v>307.79</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1313</v>
+      </c>
+      <c r="L67" t="n">
+        <v>117</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:05.212</t>
+          <t>2026-05-29 09:42:27.711</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779422047501</v>
+        <v>1780022546595</v>
       </c>
       <c r="C68" t="n">
-        <v>86843</v>
+        <v>81105</v>
       </c>
       <c r="D68" t="n">
-        <v>493.4</v>
+        <v>-756.3200000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F68" t="n">
-        <v>927</v>
+        <v>719</v>
       </c>
       <c r="G68" t="n">
-        <v>95.73</v>
+        <v>281.98</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1115</v>
+      </c>
+      <c r="L68" t="n">
+        <v>102</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.639</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:05.743</t>
+          <t>2026-05-29 09:42:27.713</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779422047703</v>
+        <v>1780022546795</v>
       </c>
       <c r="C69" t="n">
-        <v>86037</v>
+        <v>81041</v>
       </c>
       <c r="D69" t="n">
-        <v>-337.27</v>
+        <v>-782.51</v>
       </c>
       <c r="E69" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F69" t="n">
-        <v>806</v>
+        <v>719</v>
       </c>
       <c r="G69" t="n">
-        <v>94.76000000000001</v>
+        <v>281.98</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>917</v>
+      </c>
+      <c r="L69" t="n">
+        <v>106</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.447</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:05.757</t>
+          <t>2026-05-29 09:42:27.920</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779422047904</v>
+        <v>1780022546995</v>
       </c>
       <c r="C70" t="n">
-        <v>86280</v>
+        <v>80798</v>
       </c>
       <c r="D70" t="n">
-        <v>-77.41</v>
+        <v>-986.38</v>
       </c>
       <c r="E70" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F70" t="n">
-        <v>806</v>
+        <v>719</v>
       </c>
       <c r="G70" t="n">
-        <v>94.76000000000001</v>
+        <v>281.98</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K70" t="n">
+        <v>924</v>
+      </c>
+      <c r="L70" t="n">
+        <v>110</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.138</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:06.030</t>
+          <t>2026-05-29 09:42:27.975</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779422048106</v>
+        <v>1780022547195</v>
       </c>
       <c r="C71" t="n">
-        <v>86507</v>
+        <v>81442</v>
       </c>
       <c r="D71" t="n">
-        <v>153.46</v>
+        <v>-293.06</v>
       </c>
       <c r="E71" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F71" t="n">
-        <v>806</v>
+        <v>719</v>
       </c>
       <c r="G71" t="n">
-        <v>94.76000000000001</v>
+        <v>281.98</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>779</v>
+      </c>
+      <c r="L71" t="n">
+        <v>111</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.048</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:06.032</t>
+          <t>2026-05-29 09:42:28.798</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779422048307</v>
+        <v>1780022547395</v>
       </c>
       <c r="C72" t="n">
-        <v>86812</v>
+        <v>81339</v>
       </c>
       <c r="D72" t="n">
-        <v>450.79</v>
+        <v>-381.41</v>
       </c>
       <c r="E72" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F72" t="n">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="G72" t="n">
-        <v>98.83</v>
+        <v>281.98</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1402</v>
+      </c>
+      <c r="L72" t="n">
+        <v>114</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.252</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:06.468</t>
+          <t>2026-05-29 09:42:28.800</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779422048509</v>
+        <v>1780022547595</v>
       </c>
       <c r="C73" t="n">
-        <v>86153</v>
+        <v>81922</v>
       </c>
       <c r="D73" t="n">
-        <v>-230.75</v>
+        <v>220.66</v>
       </c>
       <c r="E73" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F73" t="n">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="G73" t="n">
-        <v>98.83</v>
+        <v>281.98</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L73" t="n">
+        <v>106</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.436</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:06.469</t>
+          <t>2026-05-29 09:42:29.337</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779422048710</v>
+        <v>1780022547814</v>
       </c>
       <c r="C74" t="n">
-        <v>86337</v>
+        <v>81263</v>
       </c>
       <c r="D74" t="n">
-        <v>-35.21</v>
+        <v>-449.37</v>
       </c>
       <c r="E74" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F74" t="n">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="G74" t="n">
-        <v>98.83</v>
+        <v>281.98</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1521</v>
+      </c>
+      <c r="L74" t="n">
+        <v>109</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.673</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:06.866</t>
+          <t>2026-05-29 09:42:29.353</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779422048911</v>
+        <v>1780022548014</v>
       </c>
       <c r="C75" t="n">
-        <v>86509</v>
+        <v>80887</v>
       </c>
       <c r="D75" t="n">
-        <v>138.55</v>
+        <v>-802.9</v>
       </c>
       <c r="E75" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F75" t="n">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="G75" t="n">
-        <v>98.83</v>
+        <v>281.98</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1337</v>
+      </c>
+      <c r="L75" t="n">
+        <v>107</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.339</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:06.874</t>
+          <t>2026-05-29 09:42:29.355</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779422049113</v>
+        <v>1780022548214</v>
       </c>
       <c r="C76" t="n">
-        <v>86485</v>
+        <v>80737</v>
       </c>
       <c r="D76" t="n">
-        <v>107.62</v>
+        <v>-912.76</v>
       </c>
       <c r="E76" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F76" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G76" t="n">
-        <v>98.04000000000001</v>
+        <v>281.98</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L76" t="n">
+        <v>106</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.191</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:07.396</t>
+          <t>2026-05-29 09:42:29.357</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779422049314</v>
+        <v>1780022548414</v>
       </c>
       <c r="C77" t="n">
-        <v>86247</v>
+        <v>80449</v>
       </c>
       <c r="D77" t="n">
-        <v>-135.76</v>
+        <v>-1155.12</v>
       </c>
       <c r="E77" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F77" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G77" t="n">
-        <v>98.04000000000001</v>
+        <v>281.98</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>942</v>
+      </c>
+      <c r="L77" t="n">
+        <v>105</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:07.403</t>
+          <t>2026-05-29 09:42:29.603</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779422049516</v>
+        <v>1780022548614</v>
       </c>
       <c r="C78" t="n">
-        <v>86386</v>
+        <v>80543</v>
       </c>
       <c r="D78" t="n">
-        <v>10.03</v>
+        <v>-1003.36</v>
       </c>
       <c r="E78" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F78" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G78" t="n">
-        <v>98.04000000000001</v>
+        <v>281.98</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>987</v>
+      </c>
+      <c r="L78" t="n">
+        <v>107</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.594</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:07.690</t>
+          <t>2026-05-29 09:42:29.605</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779422049717</v>
+        <v>1780022548814</v>
       </c>
       <c r="C79" t="n">
-        <v>86586</v>
+        <v>80087</v>
       </c>
       <c r="D79" t="n">
-        <v>209.53</v>
+        <v>-1409.2</v>
       </c>
       <c r="E79" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F79" t="n">
-        <v>685</v>
+        <v>719</v>
       </c>
       <c r="G79" t="n">
-        <v>101.45</v>
+        <v>281.98</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J79" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K79" t="n">
+        <v>790</v>
+      </c>
+      <c r="L79" t="n">
+        <v>112</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:07.693</t>
+          <t>2026-05-29 09:42:29.983</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779422049919</v>
+        <v>1780022549014</v>
       </c>
       <c r="C80" t="n">
-        <v>86045</v>
+        <v>80543</v>
       </c>
       <c r="D80" t="n">
-        <v>-341.95</v>
+        <v>-882.74</v>
       </c>
       <c r="E80" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F80" t="n">
-        <v>685</v>
+        <v>719</v>
       </c>
       <c r="G80" t="n">
-        <v>101.45</v>
+        <v>281.98</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K80" t="n">
+        <v>968</v>
+      </c>
+      <c r="L80" t="n">
+        <v>109</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.789</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:08.082</t>
+          <t>2026-05-29 09:42:30.014</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779422050120</v>
+        <v>1780022549214</v>
       </c>
       <c r="C81" t="n">
-        <v>86239</v>
+        <v>80244</v>
       </c>
       <c r="D81" t="n">
-        <v>-130.85</v>
+        <v>-1137.6</v>
       </c>
       <c r="E81" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F81" t="n">
-        <v>685</v>
+        <v>2619</v>
       </c>
       <c r="G81" t="n">
-        <v>101.45</v>
+        <v>281.98</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>798</v>
+      </c>
+      <c r="L81" t="n">
+        <v>107</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.036</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:08.084</t>
+          <t>2026-05-29 09:42:30.711</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779422050321</v>
+        <v>1780022549433</v>
       </c>
       <c r="C82" t="n">
-        <v>86368</v>
+        <v>80400</v>
       </c>
       <c r="D82" t="n">
-        <v>4.69</v>
+        <v>-924.72</v>
       </c>
       <c r="E82" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F82" t="n">
-        <v>685</v>
+        <v>2619</v>
       </c>
       <c r="G82" t="n">
-        <v>101.45</v>
+        <v>281.98</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L82" t="n">
+        <v>117</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.008</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:08.488</t>
+          <t>2026-05-29 09:42:30.712</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779422050523</v>
+        <v>1780022549633</v>
       </c>
       <c r="C83" t="n">
-        <v>86596</v>
+        <v>80163</v>
       </c>
       <c r="D83" t="n">
-        <v>232.46</v>
+        <v>-1115.48</v>
       </c>
       <c r="E83" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F83" t="n">
-        <v>806</v>
+        <v>2619</v>
       </c>
       <c r="G83" t="n">
-        <v>92.09</v>
+        <v>281.98</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L83" t="n">
+        <v>113</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.596</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:08.518</t>
+          <t>2026-05-29 09:42:31.705</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779422050724</v>
+        <v>1780022549833</v>
       </c>
       <c r="C84" t="n">
-        <v>85908</v>
+        <v>80071</v>
       </c>
       <c r="D84" t="n">
-        <v>-467.17</v>
+        <v>-1151.71</v>
       </c>
       <c r="E84" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F84" t="n">
-        <v>806</v>
+        <v>2619</v>
       </c>
       <c r="G84" t="n">
-        <v>92.09</v>
+        <v>281.98</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1870</v>
+      </c>
+      <c r="L84" t="n">
+        <v>115</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.175</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:09.552</t>
+          <t>2026-05-29 09:42:31.752</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779422050926</v>
+        <v>1780022550033</v>
       </c>
       <c r="C85" t="n">
-        <v>86168</v>
+        <v>79860</v>
       </c>
       <c r="D85" t="n">
-        <v>-183.81</v>
+        <v>-1305.12</v>
       </c>
       <c r="E85" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F85" t="n">
-        <v>806</v>
+        <v>2619</v>
       </c>
       <c r="G85" t="n">
-        <v>92.09</v>
+        <v>281.98</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1718</v>
+      </c>
+      <c r="L85" t="n">
+        <v>108</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.997</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:09.553</t>
+          <t>2026-05-29 09:42:31.907</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779422051127</v>
+        <v>1780022550233</v>
       </c>
       <c r="C86" t="n">
-        <v>86441</v>
+        <v>79726</v>
       </c>
       <c r="D86" t="n">
-        <v>98.38</v>
+        <v>-1373.87</v>
       </c>
       <c r="E86" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F86" t="n">
-        <v>806</v>
+        <v>2619</v>
       </c>
       <c r="G86" t="n">
-        <v>92.09</v>
+        <v>281.98</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1673</v>
+      </c>
+      <c r="L86" t="n">
+        <v>118</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.409</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:09.842</t>
+          <t>2026-05-29 09:42:31.954</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779422051329</v>
+        <v>1780022550433</v>
       </c>
       <c r="C87" t="n">
-        <v>86533</v>
+        <v>79597</v>
       </c>
       <c r="D87" t="n">
-        <v>185.46</v>
+        <v>-1434.17</v>
       </c>
       <c r="E87" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F87" t="n">
-        <v>684</v>
+        <v>2619</v>
       </c>
       <c r="G87" t="n">
-        <v>96</v>
+        <v>281.98</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1519</v>
+      </c>
+      <c r="L87" t="n">
+        <v>118</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.672</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:09.845</t>
+          <t>2026-05-29 09:42:31.984</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779422051530</v>
+        <v>1780022550633</v>
       </c>
       <c r="C88" t="n">
-        <v>85957</v>
+        <v>79819</v>
       </c>
       <c r="D88" t="n">
-        <v>-399.81</v>
+        <v>-1140.47</v>
       </c>
       <c r="E88" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F88" t="n">
-        <v>684</v>
+        <v>2619</v>
       </c>
       <c r="G88" t="n">
-        <v>96</v>
+        <v>281.98</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1349</v>
+      </c>
+      <c r="L88" t="n">
+        <v>114</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.487</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:09.846</t>
+          <t>2026-05-29 09:42:32.030</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779422051732</v>
+        <v>1780022550833</v>
       </c>
       <c r="C89" t="n">
-        <v>86178</v>
+        <v>80091</v>
       </c>
       <c r="D89" t="n">
-        <v>-158.82</v>
+        <v>-811.4400000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F89" t="n">
-        <v>684</v>
+        <v>1639</v>
       </c>
       <c r="G89" t="n">
-        <v>96</v>
+        <v>281.98</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L89" t="n">
+        <v>110</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.396</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:09.847</t>
+          <t>2026-05-29 09:42:32.408</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779422051933</v>
+        <v>1780022551052</v>
       </c>
       <c r="C90" t="n">
-        <v>86456</v>
+        <v>79740</v>
       </c>
       <c r="D90" t="n">
-        <v>127.12</v>
+        <v>-1121.87</v>
       </c>
       <c r="E90" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F90" t="n">
-        <v>786</v>
+        <v>1639</v>
       </c>
       <c r="G90" t="n">
-        <v>96.03</v>
+        <v>281.98</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1356</v>
+      </c>
+      <c r="L90" t="n">
+        <v>110</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.628</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:10.153</t>
+          <t>2026-05-29 09:42:32.410</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779422052134</v>
+        <v>1780022551252</v>
       </c>
       <c r="C91" t="n">
-        <v>86514</v>
+        <v>79909</v>
       </c>
       <c r="D91" t="n">
-        <v>178.77</v>
+        <v>-896.78</v>
       </c>
       <c r="E91" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F91" t="n">
-        <v>786</v>
+        <v>1639</v>
       </c>
       <c r="G91" t="n">
-        <v>96.03</v>
+        <v>281.98</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J91" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L91" t="n">
+        <v>118</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.637</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:10.155</t>
+          <t>2026-05-29 09:42:32.411</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779422052336</v>
+        <v>1780022551452</v>
       </c>
       <c r="C92" t="n">
-        <v>86052</v>
+        <v>79905</v>
       </c>
       <c r="D92" t="n">
-        <v>-292.17</v>
+        <v>-855.9400000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F92" t="n">
-        <v>786</v>
+        <v>1639</v>
       </c>
       <c r="G92" t="n">
-        <v>96.03</v>
+        <v>281.98</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>958</v>
+      </c>
+      <c r="L92" t="n">
+        <v>137</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.531</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:10.816</t>
+          <t>2026-05-29 09:42:32.672</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779422052537</v>
+        <v>1780022551652</v>
       </c>
       <c r="C93" t="n">
-        <v>86223</v>
+        <v>79980</v>
       </c>
       <c r="D93" t="n">
-        <v>-106.56</v>
+        <v>-738.14</v>
       </c>
       <c r="E93" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F93" t="n">
-        <v>786</v>
+        <v>819</v>
       </c>
       <c r="G93" t="n">
-        <v>96.03</v>
+        <v>271.88</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1018</v>
+      </c>
+      <c r="L93" t="n">
+        <v>107</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.243</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:10.844</t>
+          <t>2026-05-29 09:42:32.675</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779422052739</v>
+        <v>1780022551852</v>
       </c>
       <c r="C94" t="n">
-        <v>86507</v>
+        <v>79752</v>
       </c>
       <c r="D94" t="n">
-        <v>182.76</v>
+        <v>-929.23</v>
       </c>
       <c r="E94" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F94" t="n">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="G94" t="n">
-        <v>90.48999999999999</v>
+        <v>271.88</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>821</v>
+      </c>
+      <c r="L94" t="n">
+        <v>105</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.928</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:10.853</t>
+          <t>2026-05-29 09:42:33.147</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779422052940</v>
+        <v>1780022552052</v>
       </c>
       <c r="C95" t="n">
-        <v>85931</v>
+        <v>79878</v>
       </c>
       <c r="D95" t="n">
-        <v>-402.37</v>
+        <v>-756.77</v>
       </c>
       <c r="E95" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F95" t="n">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="G95" t="n">
-        <v>90.48999999999999</v>
+        <v>271.88</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1094</v>
+      </c>
+      <c r="L95" t="n">
+        <v>111</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.056</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:11.177</t>
+          <t>2026-05-29 09:42:33.148</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779422053141</v>
+        <v>1780022552252</v>
       </c>
       <c r="C96" t="n">
-        <v>86080</v>
+        <v>79696</v>
       </c>
       <c r="D96" t="n">
-        <v>-233.26</v>
+        <v>-900.9299999999999</v>
       </c>
       <c r="E96" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F96" t="n">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="G96" t="n">
-        <v>90.48999999999999</v>
+        <v>271.88</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>896</v>
+      </c>
+      <c r="L96" t="n">
+        <v>105</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.771</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:11.203</t>
+          <t>2026-05-29 09:42:33.439</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779422053343</v>
+        <v>1780022552471</v>
       </c>
       <c r="C97" t="n">
-        <v>86221</v>
+        <v>80161</v>
       </c>
       <c r="D97" t="n">
-        <v>-80.59</v>
+        <v>-390.89</v>
       </c>
       <c r="E97" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F97" t="n">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="G97" t="n">
-        <v>90.48999999999999</v>
+        <v>271.88</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K97" t="n">
+        <v>967</v>
+      </c>
+      <c r="L97" t="n">
+        <v>111</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.465</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:11.560</t>
+          <t>2026-05-29 09:42:33.495</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779422053544</v>
+        <v>1780022552671</v>
       </c>
       <c r="C98" t="n">
-        <v>86426</v>
+        <v>80373</v>
       </c>
       <c r="D98" t="n">
-        <v>128.44</v>
+        <v>-159.34</v>
       </c>
       <c r="E98" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F98" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
       <c r="G98" t="n">
-        <v>73.7</v>
+        <v>271.41</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>823</v>
+      </c>
+      <c r="L98" t="n">
+        <v>106</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.172</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:11.576</t>
+          <t>2026-05-29 09:42:34.075</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779422053746</v>
+        <v>1780022552871</v>
       </c>
       <c r="C99" t="n">
-        <v>85770</v>
+        <v>80424</v>
       </c>
       <c r="D99" t="n">
-        <v>-533.99</v>
+        <v>-100.38</v>
       </c>
       <c r="E99" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F99" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
       <c r="G99" t="n">
-        <v>73.7</v>
+        <v>271.41</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1202</v>
+      </c>
+      <c r="L99" t="n">
+        <v>110</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.462</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:11.997</t>
+          <t>2026-05-29 09:42:34.078</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779422053947</v>
+        <v>1780022553071</v>
       </c>
       <c r="C100" t="n">
-        <v>86027</v>
+        <v>80301</v>
       </c>
       <c r="D100" t="n">
-        <v>-250.29</v>
+        <v>-218.36</v>
       </c>
       <c r="E100" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F100" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
       <c r="G100" t="n">
-        <v>73.7</v>
+        <v>271.41</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1006</v>
+      </c>
+      <c r="L100" t="n">
+        <v>105</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.425</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:12.010</t>
+          <t>2026-05-29 09:42:34.331</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779422054149</v>
+        <v>1780022553271</v>
       </c>
       <c r="C101" t="n">
-        <v>86277</v>
+        <v>80515</v>
       </c>
       <c r="D101" t="n">
-        <v>12.23</v>
+        <v>6.56</v>
       </c>
       <c r="E101" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F101" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
       <c r="G101" t="n">
-        <v>73.7</v>
+        <v>271.41</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1059</v>
+      </c>
+      <c r="L101" t="n">
+        <v>108</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.571</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:12.396</t>
+          <t>2026-05-29 09:42:34.332</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779422054350</v>
+        <v>1780022553471</v>
       </c>
       <c r="C102" t="n">
-        <v>86455</v>
+        <v>80399</v>
       </c>
       <c r="D102" t="n">
-        <v>189.62</v>
+        <v>-109.77</v>
       </c>
       <c r="E102" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F102" t="n">
-        <v>705</v>
+        <v>879</v>
       </c>
       <c r="G102" t="n">
-        <v>50.89</v>
+        <v>271.41</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>860</v>
+      </c>
+      <c r="L102" t="n">
+        <v>106</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.494</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:12.397</t>
+          <t>2026-05-29 09:42:34.680</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779422054551</v>
+        <v>1780022553671</v>
       </c>
       <c r="C103" t="n">
-        <v>85826</v>
+        <v>80308</v>
       </c>
       <c r="D103" t="n">
-        <v>-448.86</v>
+        <v>-195.28</v>
       </c>
       <c r="E103" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F103" t="n">
-        <v>705</v>
+        <v>879</v>
       </c>
       <c r="G103" t="n">
-        <v>50.89</v>
+        <v>271.41</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1008</v>
+      </c>
+      <c r="L103" t="n">
+        <v>108</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:12.864</t>
+          <t>2026-05-29 09:42:34.702</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779422054753</v>
+        <v>1780022553871</v>
       </c>
       <c r="C104" t="n">
-        <v>86121</v>
+        <v>80373</v>
       </c>
       <c r="D104" t="n">
-        <v>-131.42</v>
+        <v>-120.51</v>
       </c>
       <c r="E104" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F104" t="n">
-        <v>705</v>
+        <v>879</v>
       </c>
       <c r="G104" t="n">
-        <v>50.89</v>
+        <v>271.41</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>830</v>
+      </c>
+      <c r="L104" t="n">
+        <v>107</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.002</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:12.866</t>
+          <t>2026-05-29 09:42:34.930</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779422054954</v>
+        <v>1780022554090</v>
       </c>
       <c r="C105" t="n">
-        <v>86427</v>
+        <v>80340</v>
       </c>
       <c r="D105" t="n">
-        <v>181.15</v>
+        <v>-147.49</v>
       </c>
       <c r="E105" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F105" t="n">
-        <v>725</v>
+        <v>879</v>
       </c>
       <c r="G105" t="n">
-        <v>46.79</v>
+        <v>271.41</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K105" t="n">
+        <v>838</v>
+      </c>
+      <c r="L105" t="n">
+        <v>115</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.877</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:13.215</t>
+          <t>2026-05-29 09:42:35.544</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779422055156</v>
+        <v>1780022554290</v>
       </c>
       <c r="C106" t="n">
-        <v>86473</v>
+        <v>79477</v>
       </c>
       <c r="D106" t="n">
-        <v>218.09</v>
+        <v>-1003.11</v>
       </c>
       <c r="E106" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F106" t="n">
-        <v>725</v>
+        <v>879</v>
       </c>
       <c r="G106" t="n">
-        <v>46.79</v>
+        <v>271.41</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L106" t="n">
+        <v>112</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.822</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:13.216</t>
+          <t>2026-05-29 09:42:35.546</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779422055357</v>
+        <v>1780022554490</v>
       </c>
       <c r="C107" t="n">
-        <v>85917</v>
+        <v>79252</v>
       </c>
       <c r="D107" t="n">
-        <v>-348.81</v>
+        <v>-1177.96</v>
       </c>
       <c r="E107" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F107" t="n">
-        <v>725</v>
+        <v>879</v>
       </c>
       <c r="G107" t="n">
-        <v>46.79</v>
+        <v>271.41</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1055</v>
+      </c>
+      <c r="L107" t="n">
+        <v>103</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.995</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:13.650</t>
+          <t>2026-05-29 09:42:36.106</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779422055558</v>
+        <v>1780022554690</v>
       </c>
       <c r="C108" t="n">
-        <v>86124</v>
+        <v>79027</v>
       </c>
       <c r="D108" t="n">
-        <v>-124.37</v>
+        <v>-1344.06</v>
       </c>
       <c r="E108" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F108" t="n">
-        <v>725</v>
+        <v>879</v>
       </c>
       <c r="G108" t="n">
-        <v>46.79</v>
+        <v>271.41</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1414</v>
+      </c>
+      <c r="L108" t="n">
+        <v>116</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.698</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:13.652</t>
+          <t>2026-05-29 09:42:36.121</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779422055760</v>
+        <v>1780022554890</v>
       </c>
       <c r="C109" t="n">
-        <v>86352</v>
+        <v>79102</v>
       </c>
       <c r="D109" t="n">
-        <v>109.85</v>
+        <v>-1201.86</v>
       </c>
       <c r="E109" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F109" t="n">
-        <v>725</v>
+        <v>879</v>
       </c>
       <c r="G109" t="n">
-        <v>46.79</v>
+        <v>271.41</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L109" t="n">
+        <v>103</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.987</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:14.027</t>
+          <t>2026-05-29 09:42:36.141</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779422055961</v>
+        <v>1780022555090</v>
       </c>
       <c r="C110" t="n">
-        <v>86002</v>
+        <v>79495</v>
       </c>
       <c r="D110" t="n">
-        <v>-245.64</v>
+        <v>-748.76</v>
       </c>
       <c r="E110" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F110" t="n">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="G110" t="n">
-        <v>59.65</v>
+        <v>271.41</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1049</v>
+      </c>
+      <c r="L110" t="n">
+        <v>104</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.731</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:14.041</t>
+          <t>2026-05-29 09:42:36.340</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779422056163</v>
+        <v>1780022555290</v>
       </c>
       <c r="C111" t="n">
-        <v>86066</v>
+        <v>80136</v>
       </c>
       <c r="D111" t="n">
-        <v>-169.36</v>
+        <v>-70.33</v>
       </c>
       <c r="E111" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F111" t="n">
-        <v>866</v>
+        <v>2639</v>
       </c>
       <c r="G111" t="n">
-        <v>59.65</v>
+        <v>271.41</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1049</v>
+      </c>
+      <c r="L111" t="n">
+        <v>117</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:14.456</t>
+          <t>2026-05-29 09:42:36.342</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779422056364</v>
+        <v>1780022555490</v>
       </c>
       <c r="C112" t="n">
-        <v>86235</v>
+        <v>79540</v>
       </c>
       <c r="D112" t="n">
-        <v>8.109999999999999</v>
+        <v>-662.8099999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F112" t="n">
-        <v>866</v>
+        <v>2639</v>
       </c>
       <c r="G112" t="n">
-        <v>59.65</v>
+        <v>271.41</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>851</v>
+      </c>
+      <c r="L112" t="n">
+        <v>119</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.134</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:14.457</t>
+          <t>2026-05-29 09:42:37.065</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779422056565</v>
+        <v>1780022555690</v>
       </c>
       <c r="C113" t="n">
-        <v>86435</v>
+        <v>79903</v>
       </c>
       <c r="D113" t="n">
-        <v>207.7</v>
+        <v>-266.67</v>
       </c>
       <c r="E113" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F113" t="n">
-        <v>685</v>
+        <v>2639</v>
       </c>
       <c r="G113" t="n">
-        <v>63.68</v>
+        <v>271.41</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1374</v>
+      </c>
+      <c r="L113" t="n">
+        <v>112</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.007</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:14.894</t>
+          <t>2026-05-29 09:42:37.066</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779422056767</v>
+        <v>1780022555909</v>
       </c>
       <c r="C114" t="n">
-        <v>85799</v>
+        <v>78751</v>
       </c>
       <c r="D114" t="n">
-        <v>-438.68</v>
+        <v>-1405.34</v>
       </c>
       <c r="E114" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F114" t="n">
-        <v>685</v>
+        <v>2639</v>
       </c>
       <c r="G114" t="n">
-        <v>63.68</v>
+        <v>271.41</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1156</v>
+      </c>
+      <c r="L114" t="n">
+        <v>108</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.993</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:14.899</t>
+          <t>2026-05-29 09:42:37.520</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779422056968</v>
+        <v>1780022556109</v>
       </c>
       <c r="C115" t="n">
-        <v>85914</v>
+        <v>78778</v>
       </c>
       <c r="D115" t="n">
-        <v>-301.75</v>
+        <v>-1308.07</v>
       </c>
       <c r="E115" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F115" t="n">
-        <v>685</v>
+        <v>2639</v>
       </c>
       <c r="G115" t="n">
-        <v>63.68</v>
+        <v>271.41</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1410</v>
+      </c>
+      <c r="L115" t="n">
+        <v>122</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.968</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:15.261</t>
+          <t>2026-05-29 09:42:37.522</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779422057170</v>
+        <v>1780022556309</v>
       </c>
       <c r="C116" t="n">
-        <v>86163</v>
+        <v>76999</v>
       </c>
       <c r="D116" t="n">
-        <v>-37.66</v>
+        <v>-3021.67</v>
       </c>
       <c r="E116" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F116" t="n">
-        <v>685</v>
+        <v>2639</v>
       </c>
       <c r="G116" t="n">
-        <v>63.68</v>
+        <v>271.41</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1212</v>
+      </c>
+      <c r="L116" t="n">
+        <v>110</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.926</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:15.262</t>
+          <t>2026-05-29 09:42:37.523</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779422057371</v>
+        <v>1780022556509</v>
       </c>
       <c r="C117" t="n">
-        <v>86411</v>
+        <v>77491</v>
       </c>
       <c r="D117" t="n">
-        <v>212.22</v>
+        <v>-2378.58</v>
       </c>
       <c r="E117" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F117" t="n">
-        <v>826</v>
+        <v>2639</v>
       </c>
       <c r="G117" t="n">
-        <v>63.47</v>
+        <v>271.41</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L117" t="n">
+        <v>111</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.898</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:15.689</t>
+          <t>2026-05-29 09:42:37.909</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779422057572</v>
+        <v>1780022556709</v>
       </c>
       <c r="C118" t="n">
-        <v>85758</v>
+        <v>78766</v>
       </c>
       <c r="D118" t="n">
-        <v>-451.39</v>
+        <v>-984.65</v>
       </c>
       <c r="E118" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F118" t="n">
-        <v>826</v>
+        <v>2639</v>
       </c>
       <c r="G118" t="n">
-        <v>63.47</v>
+        <v>271.41</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1199</v>
+      </c>
+      <c r="L118" t="n">
+        <v>115</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.191</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:15.690</t>
+          <t>2026-05-29 09:42:37.910</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779422057774</v>
+        <v>1780022556909</v>
       </c>
       <c r="C119" t="n">
-        <v>85970</v>
+        <v>78680</v>
       </c>
       <c r="D119" t="n">
-        <v>-216.82</v>
+        <v>-1021.42</v>
       </c>
       <c r="E119" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F119" t="n">
-        <v>826</v>
+        <v>2639</v>
       </c>
       <c r="G119" t="n">
-        <v>63.47</v>
+        <v>271.41</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L119" t="n">
+        <v>107</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.855</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:16.083</t>
+          <t>2026-05-29 09:42:37.911</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779422057975</v>
+        <v>1780022557109</v>
       </c>
       <c r="C120" t="n">
-        <v>86180</v>
+        <v>78914</v>
       </c>
       <c r="D120" t="n">
-        <v>4.02</v>
+        <v>-736.35</v>
       </c>
       <c r="E120" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F120" t="n">
-        <v>826</v>
+        <v>2639</v>
       </c>
       <c r="G120" t="n">
-        <v>63.47</v>
+        <v>271.41</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K120" t="n">
+        <v>802</v>
+      </c>
+      <c r="L120" t="n">
+        <v>103</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.885</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:16.112</t>
+          <t>2026-05-29 09:42:38.172</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779422058177</v>
+        <v>1780022557309</v>
       </c>
       <c r="C121" t="n">
-        <v>86421</v>
+        <v>78348</v>
       </c>
       <c r="D121" t="n">
-        <v>244.82</v>
+        <v>-1265.53</v>
       </c>
       <c r="E121" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F121" t="n">
-        <v>785</v>
+        <v>2639</v>
       </c>
       <c r="G121" t="n">
-        <v>62.24</v>
+        <v>271.41</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K121" t="n">
+        <v>862</v>
+      </c>
+      <c r="L121" t="n">
+        <v>118</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.571</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:16.613</t>
+          <t>2026-05-29 09:42:39.493</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779422058378</v>
+        <v>1780022557509</v>
       </c>
       <c r="C122" t="n">
-        <v>85781</v>
+        <v>78531</v>
       </c>
       <c r="D122" t="n">
-        <v>-407.42</v>
+        <v>-1019.26</v>
       </c>
       <c r="E122" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F122" t="n">
-        <v>785</v>
+        <v>2639</v>
       </c>
       <c r="G122" t="n">
-        <v>62.24</v>
+        <v>271.41</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1983</v>
+      </c>
+      <c r="L122" t="n">
+        <v>127</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:16.614</t>
+          <t>2026-05-29 09:42:39.494</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779422058580</v>
+        <v>1780022557728</v>
       </c>
       <c r="C123" t="n">
-        <v>86186</v>
+        <v>77619</v>
       </c>
       <c r="D123" t="n">
-        <v>17.95</v>
+        <v>-1880.29</v>
       </c>
       <c r="E123" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F123" t="n">
-        <v>785</v>
+        <v>2639</v>
       </c>
       <c r="G123" t="n">
-        <v>62.24</v>
+        <v>271.41</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1766</v>
+      </c>
+      <c r="L123" t="n">
+        <v>118</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.912</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:16.953</t>
+          <t>2026-05-29 09:42:39.496</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779422058781</v>
+        <v>1780022557928</v>
       </c>
       <c r="C124" t="n">
-        <v>86324</v>
+        <v>77052</v>
       </c>
       <c r="D124" t="n">
-        <v>155.05</v>
+        <v>-2353.28</v>
       </c>
       <c r="E124" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F124" t="n">
-        <v>785</v>
+        <v>2639</v>
       </c>
       <c r="G124" t="n">
-        <v>62.24</v>
+        <v>271.41</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1567</v>
+      </c>
+      <c r="L124" t="n">
+        <v>106</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.926</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:16.976</t>
+          <t>2026-05-29 09:42:39.497</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779422058982</v>
+        <v>1780022558128</v>
       </c>
       <c r="C125" t="n">
-        <v>86499</v>
+        <v>76498</v>
       </c>
       <c r="D125" t="n">
-        <v>322.3</v>
+        <v>-2789.61</v>
       </c>
       <c r="E125" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F125" t="n">
-        <v>725</v>
+        <v>2639</v>
       </c>
       <c r="G125" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1368</v>
+      </c>
+      <c r="L125" t="n">
+        <v>105</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:17.293</t>
+          <t>2026-05-29 09:42:39.498</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779422059184</v>
+        <v>1780022558328</v>
       </c>
       <c r="C126" t="n">
-        <v>85875</v>
+        <v>78221</v>
       </c>
       <c r="D126" t="n">
-        <v>-317.82</v>
+        <v>-927.13</v>
       </c>
       <c r="E126" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F126" t="n">
-        <v>725</v>
+        <v>2639</v>
       </c>
       <c r="G126" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1169</v>
+      </c>
+      <c r="L126" t="n">
+        <v>105</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.967</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:17.294</t>
+          <t>2026-05-29 09:42:39.499</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779422059385</v>
+        <v>1780022558528</v>
       </c>
       <c r="C127" t="n">
-        <v>86132</v>
+        <v>79277</v>
       </c>
       <c r="D127" t="n">
-        <v>-44.93</v>
+        <v>175.22</v>
       </c>
       <c r="E127" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F127" t="n">
-        <v>725</v>
+        <v>2639</v>
       </c>
       <c r="G127" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>970</v>
+      </c>
+      <c r="L127" t="n">
+        <v>111</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.616</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:17.295</t>
+          <t>2026-05-29 09:42:39.836</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779422059587</v>
+        <v>1780022558728</v>
       </c>
       <c r="C128" t="n">
-        <v>86410</v>
+        <v>80921</v>
       </c>
       <c r="D128" t="n">
-        <v>235.32</v>
+        <v>1810.46</v>
       </c>
       <c r="E128" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F128" t="n">
-        <v>725</v>
+        <v>2639</v>
       </c>
       <c r="G128" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L128" t="n">
+        <v>105</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.996</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:17.716</t>
+          <t>2026-05-29 09:42:39.837</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779422059788</v>
+        <v>1780022558928</v>
       </c>
       <c r="C129" t="n">
-        <v>86366</v>
+        <v>80976</v>
       </c>
       <c r="D129" t="n">
-        <v>179.55</v>
+        <v>1774.94</v>
       </c>
       <c r="E129" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F129" t="n">
-        <v>806</v>
+        <v>2639</v>
       </c>
       <c r="G129" t="n">
-        <v>58.9</v>
+        <v>271.41</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K129" t="n">
+        <v>908</v>
+      </c>
+      <c r="L129" t="n">
+        <v>117</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.165</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:17.718</t>
+          <t>2026-05-29 09:42:41.236</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779422059989</v>
+        <v>1780022559128</v>
       </c>
       <c r="C130" t="n">
-        <v>86018</v>
+        <v>80240</v>
       </c>
       <c r="D130" t="n">
-        <v>-177.42</v>
+        <v>950.1900000000001</v>
       </c>
       <c r="E130" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F130" t="n">
-        <v>806</v>
+        <v>2639</v>
       </c>
       <c r="G130" t="n">
-        <v>58.9</v>
+        <v>271.41</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K130" t="n">
+        <v>2107</v>
+      </c>
+      <c r="L130" t="n">
+        <v>117</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.562</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:18.132</t>
+          <t>2026-05-29 09:42:41.238</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779422060191</v>
+        <v>1780022559347</v>
       </c>
       <c r="C131" t="n">
-        <v>86211</v>
+        <v>80353</v>
       </c>
       <c r="D131" t="n">
-        <v>24.45</v>
+        <v>1015.68</v>
       </c>
       <c r="E131" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F131" t="n">
-        <v>806</v>
+        <v>2639</v>
       </c>
       <c r="G131" t="n">
-        <v>58.9</v>
+        <v>271.41</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1890</v>
+      </c>
+      <c r="L131" t="n">
+        <v>120</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.469</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:18.134</t>
+          <t>2026-05-29 09:42:41.240</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779422060392</v>
+        <v>1780022559547</v>
       </c>
       <c r="C132" t="n">
-        <v>86482</v>
+        <v>80187</v>
       </c>
       <c r="D132" t="n">
-        <v>294.23</v>
+        <v>798.9</v>
       </c>
       <c r="E132" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F132" t="n">
-        <v>745</v>
+        <v>2639</v>
       </c>
       <c r="G132" t="n">
-        <v>57.61</v>
+        <v>271.41</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1692</v>
+      </c>
+      <c r="L132" t="n">
+        <v>121</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1.327</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:18.617</t>
+          <t>2026-05-29 09:42:41.241</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779422060594</v>
+        <v>1780022559747</v>
       </c>
       <c r="C133" t="n">
-        <v>86067</v>
+        <v>81061</v>
       </c>
       <c r="D133" t="n">
-        <v>-135.49</v>
+        <v>1632.95</v>
       </c>
       <c r="E133" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F133" t="n">
-        <v>745</v>
+        <v>2639</v>
       </c>
       <c r="G133" t="n">
-        <v>57.61</v>
+        <v>271.41</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1493</v>
+      </c>
+      <c r="L133" t="n">
+        <v>121</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.713</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:18.618</t>
+          <t>2026-05-29 09:42:41.241</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779422060795</v>
+        <v>1780022559947</v>
       </c>
       <c r="C134" t="n">
-        <v>86037</v>
+        <v>81149</v>
       </c>
       <c r="D134" t="n">
-        <v>-158.71</v>
+        <v>1639.31</v>
       </c>
       <c r="E134" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F134" t="n">
-        <v>745</v>
+        <v>2639</v>
       </c>
       <c r="G134" t="n">
-        <v>57.61</v>
+        <v>271.41</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1294</v>
+      </c>
+      <c r="L134" t="n">
+        <v>106</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.548</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:18.930</t>
+          <t>2026-05-29 09:42:41.242</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779422060997</v>
+        <v>1780022560147</v>
       </c>
       <c r="C135" t="n">
-        <v>86223</v>
+        <v>81260</v>
       </c>
       <c r="D135" t="n">
-        <v>35.22</v>
+        <v>1668.34</v>
       </c>
       <c r="E135" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F135" t="n">
-        <v>745</v>
+        <v>2639</v>
       </c>
       <c r="G135" t="n">
-        <v>57.61</v>
+        <v>271.41</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L135" t="n">
+        <v>111</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:18.960</t>
+          <t>2026-05-29 09:42:41.498</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779422061198</v>
+        <v>1780022560347</v>
       </c>
       <c r="C136" t="n">
-        <v>86501</v>
+        <v>81283</v>
       </c>
       <c r="D136" t="n">
-        <v>311.46</v>
+        <v>1607.92</v>
       </c>
       <c r="E136" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F136" t="n">
-        <v>786</v>
+        <v>2639</v>
       </c>
       <c r="G136" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1149</v>
+      </c>
+      <c r="L136" t="n">
+        <v>109</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.381</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:19.361</t>
+          <t>2026-05-29 09:42:41.505</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779422061399</v>
+        <v>1780022560547</v>
       </c>
       <c r="C137" t="n">
-        <v>86162</v>
+        <v>81907</v>
       </c>
       <c r="D137" t="n">
-        <v>-43.11</v>
+        <v>2151.53</v>
       </c>
       <c r="E137" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F137" t="n">
-        <v>786</v>
+        <v>2639</v>
       </c>
       <c r="G137" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J137" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K137" t="n">
+        <v>956</v>
+      </c>
+      <c r="L137" t="n">
+        <v>115</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.623</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:19.374</t>
+          <t>2026-05-29 09:42:41.959</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779422061601</v>
+        <v>1780022560748</v>
       </c>
       <c r="C138" t="n">
-        <v>85942</v>
+        <v>81451</v>
       </c>
       <c r="D138" t="n">
-        <v>-260.95</v>
+        <v>1587.95</v>
       </c>
       <c r="E138" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F138" t="n">
-        <v>786</v>
+        <v>2639</v>
       </c>
       <c r="G138" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1210</v>
+      </c>
+      <c r="L138" t="n">
+        <v>107</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.979</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:19.764</t>
+          <t>2026-05-29 09:42:41.960</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779422061802</v>
+        <v>1780022560966</v>
       </c>
       <c r="C139" t="n">
-        <v>86252</v>
+        <v>81454</v>
       </c>
       <c r="D139" t="n">
-        <v>62.09</v>
+        <v>1511.55</v>
       </c>
       <c r="E139" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F139" t="n">
-        <v>786</v>
+        <v>2639</v>
       </c>
       <c r="G139" t="n">
-        <v>57.78</v>
+        <v>271.41</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>993</v>
+      </c>
+      <c r="L139" t="n">
+        <v>121</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.891</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:19.785</t>
+          <t>2026-05-29 09:42:42.464</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779422062004</v>
+        <v>1780022561167</v>
       </c>
       <c r="C140" t="n">
-        <v>86474</v>
+        <v>80549</v>
       </c>
       <c r="D140" t="n">
-        <v>280.99</v>
+        <v>530.98</v>
       </c>
       <c r="E140" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F140" t="n">
-        <v>805</v>
+        <v>2639</v>
       </c>
       <c r="G140" t="n">
-        <v>54.73</v>
+        <v>271.41</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1296</v>
+      </c>
+      <c r="L140" t="n">
+        <v>107</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:20.389</t>
+          <t>2026-05-29 09:42:42.480</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779422062205</v>
+        <v>1780022561366</v>
       </c>
       <c r="C141" t="n">
-        <v>86079</v>
+        <v>80431</v>
       </c>
       <c r="D141" t="n">
-        <v>-128.06</v>
+        <v>386.43</v>
       </c>
       <c r="E141" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F141" t="n">
-        <v>805</v>
+        <v>2639</v>
       </c>
       <c r="G141" t="n">
-        <v>54.73</v>
+        <v>271.41</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1113</v>
+      </c>
+      <c r="L141" t="n">
+        <v>112</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.269</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:20.390</t>
+          <t>2026-05-29 09:42:42.792</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1779422062406</v>
+        <v>1780022561567</v>
       </c>
       <c r="C142" t="n">
-        <v>85944</v>
+        <v>80424</v>
       </c>
       <c r="D142" t="n">
-        <v>-256.66</v>
+        <v>360.11</v>
       </c>
       <c r="E142" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F142" t="n">
-        <v>805</v>
+        <v>2639</v>
       </c>
       <c r="G142" t="n">
-        <v>54.73</v>
+        <v>271.41</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1224</v>
+      </c>
+      <c r="L142" t="n">
+        <v>107</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.008</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:20.391</t>
+          <t>2026-05-29 09:42:42.794</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1779422062608</v>
+        <v>1780022561766</v>
       </c>
       <c r="C143" t="n">
-        <v>86045</v>
+        <v>80826</v>
       </c>
       <c r="D143" t="n">
-        <v>-142.82</v>
+        <v>744.1</v>
       </c>
       <c r="E143" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F143" t="n">
-        <v>805</v>
+        <v>2639</v>
       </c>
       <c r="G143" t="n">
-        <v>54.73</v>
+        <v>271.41</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1026</v>
+      </c>
+      <c r="L143" t="n">
+        <v>108</v>
+      </c>
+      <c r="M143" t="n">
+        <v>2.008</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:20.782</t>
+          <t>2026-05-29 09:42:42.796</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1779422062809</v>
+        <v>1780022561967</v>
       </c>
       <c r="C144" t="n">
-        <v>86309</v>
+        <v>80571</v>
       </c>
       <c r="D144" t="n">
-        <v>128.32</v>
+        <v>451.9</v>
       </c>
       <c r="E144" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F144" t="n">
-        <v>805</v>
+        <v>2639</v>
       </c>
       <c r="G144" t="n">
-        <v>54.73</v>
+        <v>271.41</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K144" t="n">
+        <v>828</v>
+      </c>
+      <c r="L144" t="n">
+        <v>108</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.882</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:20.806</t>
+          <t>2026-05-29 09:42:43.311</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1779422063011</v>
+        <v>1780022562166</v>
       </c>
       <c r="C145" t="n">
-        <v>85672</v>
+        <v>80410</v>
       </c>
       <c r="D145" t="n">
-        <v>-515.1</v>
+        <v>268.3</v>
       </c>
       <c r="E145" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F145" t="n">
-        <v>886</v>
+        <v>2639</v>
       </c>
       <c r="G145" t="n">
-        <v>61.52</v>
+        <v>271.41</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1144</v>
+      </c>
+      <c r="L145" t="n">
+        <v>114</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.445</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:21.204</t>
+          <t>2026-05-29 09:42:43.352</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1779422063212</v>
+        <v>1780022562366</v>
       </c>
       <c r="C146" t="n">
-        <v>85852</v>
+        <v>80554</v>
       </c>
       <c r="D146" t="n">
-        <v>-309.34</v>
+        <v>398.89</v>
       </c>
       <c r="E146" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F146" t="n">
-        <v>886</v>
+        <v>2639</v>
       </c>
       <c r="G146" t="n">
-        <v>61.52</v>
+        <v>271.41</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K146" t="n">
+        <v>986</v>
+      </c>
+      <c r="L146" t="n">
+        <v>93</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.472</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:21.205</t>
+          <t>2026-05-29 09:42:43.571</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1779422063413</v>
+        <v>1780022562585</v>
       </c>
       <c r="C147" t="n">
-        <v>86048</v>
+        <v>80452</v>
       </c>
       <c r="D147" t="n">
-        <v>-97.88</v>
+        <v>276.94</v>
       </c>
       <c r="E147" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F147" t="n">
-        <v>886</v>
+        <v>7336</v>
       </c>
       <c r="G147" t="n">
-        <v>61.52</v>
+        <v>271.41</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K147" t="n">
+        <v>986</v>
+      </c>
+      <c r="L147" t="n">
+        <v>111</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.464</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:21.614</t>
+          <t>2026-05-29 09:42:43.972</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1779422063615</v>
+        <v>1780022562787</v>
       </c>
       <c r="C148" t="n">
-        <v>86278</v>
+        <v>80528</v>
       </c>
       <c r="D148" t="n">
-        <v>137.02</v>
+        <v>339.09</v>
       </c>
       <c r="E148" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F148" t="n">
-        <v>725</v>
+        <v>7336</v>
       </c>
       <c r="G148" t="n">
-        <v>58.64</v>
+        <v>271.41</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I148" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="J148" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1184</v>
+      </c>
+      <c r="L148" t="n">
+        <v>168</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.979</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:21.615</t>
+          <t>2026-05-29 09:42:43.973</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1779422063816</v>
+        <v>1780022563005</v>
       </c>
       <c r="C149" t="n">
-        <v>85586</v>
+        <v>81125</v>
       </c>
       <c r="D149" t="n">
-        <v>-561.83</v>
+        <v>919.14</v>
       </c>
       <c r="E149" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F149" t="n">
-        <v>725</v>
+        <v>399</v>
       </c>
       <c r="G149" t="n">
-        <v>58.64</v>
+        <v>276.92</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K149" t="n">
+        <v>967</v>
+      </c>
+      <c r="L149" t="n">
+        <v>110</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.992</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-22 10:54:22.646</t>
+          <t>2026-05-29 09:42:44.324</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1779422064018</v>
+        <v>1780022563205</v>
       </c>
       <c r="C150" t="n">
-        <v>85791</v>
+        <v>81230</v>
       </c>
       <c r="D150" t="n">
-        <v>-328.74</v>
+        <v>978.1799999999999</v>
       </c>
       <c r="E150" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F150" t="n">
-        <v>725</v>
+        <v>399</v>
       </c>
       <c r="G150" t="n">
-        <v>58.64</v>
+        <v>276.92</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1118</v>
+      </c>
+      <c r="L150" t="n">
+        <v>116</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.116</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:42:44.336</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1780022563405</v>
+      </c>
+      <c r="C151" t="n">
+        <v>81437</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1136.27</v>
+      </c>
+      <c r="E151" t="n">
+        <v>93</v>
+      </c>
+      <c r="F151" t="n">
+        <v>399</v>
+      </c>
+      <c r="G151" t="n">
+        <v>276.92</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K151" t="n">
+        <v>930</v>
+      </c>
+      <c r="L151" t="n">
+        <v>149</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1.154</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:42:45.001</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1780022563606</v>
+      </c>
+      <c r="C152" t="n">
+        <v>81367</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1009.46</v>
+      </c>
+      <c r="E152" t="n">
+        <v>93</v>
+      </c>
+      <c r="F152" t="n">
+        <v>399</v>
+      </c>
+      <c r="G152" t="n">
+        <v>276.92</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="J152" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1394</v>
+      </c>
+      <c r="L152" t="n">
+        <v>119</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1.309</v>
       </c>
     </row>
   </sheetData>
